--- a/data/trans_orig/LAWTONB_2R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16307</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34210</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53662</t>
+          <t>53959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55283</t>
+          <t>54738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73186</t>
+          <t>72088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>32227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44728</t>
+          <t>44579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41553</t>
+          <t>41190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56199</t>
+          <t>56520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35848</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>38,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44884</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>59213</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60182</t>
+          <t>59363</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77609</t>
+          <t>76620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59438</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87031</t>
+          <t>86394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33049</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81115</t>
+          <t>82313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113018</t>
+          <t>114662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173041</t>
+          <t>173678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200634</t>
+          <t>200751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52703</t>
+          <t>52884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>68342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>231162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264709</t>
+          <t>263511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26327</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46667</t>
+          <t>46527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42123</t>
+          <t>42310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65348</t>
+          <t>66257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>30964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44283</t>
+          <t>44340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49583</t>
+          <t>49723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69923</t>
+          <t>69695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86367</t>
+          <t>85458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109592</t>
+          <t>109405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>124026</t>
+          <t>126094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>163576</t>
+          <t>164526</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126215</t>
+          <t>124823</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>165674</t>
+          <t>165242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261494</t>
+          <t>260544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>301044</t>
+          <t>298976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263041</t>
+          <t>263473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>302500</t>
+          <t>303892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114906</t>
+          <t>113200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151020</t>
+          <t>153236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207894</t>
+          <t>209951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>257407</t>
+          <t>260274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332138</t>
+          <t>337533</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>396332</t>
+          <t>398705</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>350531</t>
+          <t>348315</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>386645</t>
+          <t>388351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>416568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>468948</t>
+          <t>466891</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>782061</t>
+          <t>779688</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>846255</t>
+          <t>840860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40140</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62918</t>
+          <t>63340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27783</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>43381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56538</t>
+          <t>56409</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51748</t>
+          <t>50614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68346</t>
+          <t>68870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>37913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>26189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34270</t>
+          <t>34085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59598</t>
+          <t>58603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81249</t>
+          <t>80740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101494</t>
+          <t>101157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>28426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113670</t>
+          <t>114665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138998</t>
+          <t>139183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55157</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84490</t>
+          <t>83109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31439</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78072</t>
+          <t>77670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>111034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147263</t>
+          <t>148644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176596</t>
+          <t>178806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>28756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44028</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180924</t>
+          <t>180814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213776</t>
+          <t>214178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46056</t>
+          <t>45735</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71820</t>
+          <t>71493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98604</t>
+          <t>98188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103940</t>
+          <t>105637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136392</t>
+          <t>139804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56640</t>
+          <t>56961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76162</t>
+          <t>75991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89796</t>
+          <t>90212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116580</t>
+          <t>116907</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154704</t>
+          <t>151292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>187156</t>
+          <t>185459</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126599</t>
+          <t>126425</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166641</t>
+          <t>166912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127636</t>
+          <t>126816</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167140</t>
+          <t>163998</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228063</t>
+          <t>227792</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268105</t>
+          <t>268279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>229552</t>
+          <t>232694</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269056</t>
+          <t>269876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129139</t>
+          <t>127667</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173471</t>
+          <t>172407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>257808</t>
+          <t>259328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314067</t>
+          <t>311950</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401207</t>
+          <t>401087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>469412</t>
+          <t>473420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>386166</t>
+          <t>387230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>430498</t>
+          <t>431970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>427938</t>
+          <t>430055</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>484197</t>
+          <t>482677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>832230</t>
+          <t>828222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>900435</t>
+          <t>900555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>25242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54793</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65576</t>
+          <t>65792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32714</t>
+          <t>32779</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79873</t>
+          <t>80293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96130</t>
+          <t>96412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>16970</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26987</t>
+          <t>27148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36774</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47768</t>
+          <t>47194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43945</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58714</t>
+          <t>58590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43658</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95343</t>
+          <t>95138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110377</t>
+          <t>110405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122812</t>
+          <t>122101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143693</t>
+          <t>143745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,35%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>32098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>53713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>45240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61639</t>
+          <t>61597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92834</t>
+          <t>90562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150107</t>
+          <t>150143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172338</t>
+          <t>171758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>53806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75174</t>
+          <t>75474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>210068</t>
+          <t>212340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241263</t>
+          <t>241305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>60793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68921</t>
+          <t>69022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88122</t>
+          <t>88420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121427</t>
+          <t>121748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85575</t>
+          <t>84428</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107055</t>
+          <t>106828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90629</t>
+          <t>90528</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117022</t>
+          <t>115934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183344</t>
+          <t>183023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216649</t>
+          <t>216351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>129782</t>
+          <t>131704</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172826</t>
+          <t>174469</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129782</t>
+          <t>131704</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172826</t>
+          <t>174469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240257</t>
+          <t>238614</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>283301</t>
+          <t>281379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>240257</t>
+          <t>238614</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>283301</t>
+          <t>281379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106103</t>
+          <t>105641</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142797</t>
+          <t>143942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>246395</t>
+          <t>244556</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>304693</t>
+          <t>303683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>362576</t>
+          <t>365506</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433744</t>
+          <t>441255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>448531</t>
+          <t>447386</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>485225</t>
+          <t>485687</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>467671</t>
+          <t>468681</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>525969</t>
+          <t>527808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>929948</t>
+          <t>922437</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1001116</t>
+          <t>998186</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,2%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18103</t>
+          <t>18062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>20787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88319</t>
+          <t>88360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98366</t>
+          <t>98853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44322</t>
+          <t>44574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54806</t>
+          <t>54970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136977</t>
+          <t>136632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151712</t>
+          <t>150956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>23383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>40037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71422</t>
+          <t>71615</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83675</t>
+          <t>83345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36744</t>
+          <t>36756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103694</t>
+          <t>101892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118612</t>
+          <t>117784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32198</t>
+          <t>33579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75022</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87212</t>
+          <t>87342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104172</t>
+          <t>103889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121059</t>
+          <t>119678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66967</t>
+          <t>66712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91174</t>
+          <t>90009</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108075</t>
+          <t>109422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45867</t>
+          <t>46793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190907</t>
+          <t>191239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144562</t>
+          <t>145727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168769</t>
+          <t>169024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218618</t>
+          <t>217271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317171</t>
+          <t>317125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>371522</t>
+          <t>371190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>516562</t>
+          <t>515636</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24597</t>
+          <t>25163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38863</t>
+          <t>39496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88336</t>
+          <t>88972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107345</t>
+          <t>107913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118265</t>
+          <t>119006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142140</t>
+          <t>143123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51569</t>
+          <t>50936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65835</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96064</t>
+          <t>95496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115073</t>
+          <t>114437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151701</t>
+          <t>150718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175576</t>
+          <t>174835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>133630</t>
+          <t>133301</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159150</t>
+          <t>160185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135291</t>
+          <t>136667</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>161111</t>
+          <t>162837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160700</t>
+          <t>159665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186220</t>
+          <t>186549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161943</t>
+          <t>160217</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187763</t>
+          <t>186387</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144382</t>
+          <t>145831</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178926</t>
+          <t>180819</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187639</t>
+          <t>172775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>428629</t>
+          <t>426451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>323424</t>
+          <t>318655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>577291</t>
+          <t>577143</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>453352</t>
+          <t>451459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>487896</t>
+          <t>486447</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>585345</t>
+          <t>587523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>826335</t>
+          <t>841199</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1068961</t>
+          <t>1069109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322828</t>
+          <t>1327597</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/LAWTONB_2R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34755</t>
+          <t>34792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>41147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>53863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54738</t>
+          <t>54701</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72088</t>
+          <t>72164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32227</t>
+          <t>31148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44579</t>
+          <t>44453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41190</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56520</t>
+          <t>55949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26913</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36667</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44841</t>
+          <t>44968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59213</t>
+          <t>58889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59363</t>
+          <t>59713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76620</t>
+          <t>76510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59321</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86394</t>
+          <t>87729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82313</t>
+          <t>80124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114662</t>
+          <t>111093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173678</t>
+          <t>172343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200751</t>
+          <t>200062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52884</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68342</t>
+          <t>68483</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231162</t>
+          <t>234731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>263511</t>
+          <t>265700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>26797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46527</t>
+          <t>46932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42310</t>
+          <t>41328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66257</t>
+          <t>65336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30964</t>
+          <t>32131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44340</t>
+          <t>44620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49723</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69695</t>
+          <t>69453</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85458</t>
+          <t>86379</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109405</t>
+          <t>110387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126094</t>
+          <t>124989</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>164526</t>
+          <t>165016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124823</t>
+          <t>125737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>165242</t>
+          <t>168594</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260544</t>
+          <t>260054</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298976</t>
+          <t>300081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263473</t>
+          <t>260121</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>303892</t>
+          <t>302978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113200</t>
+          <t>113675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153236</t>
+          <t>152766</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>209277</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>260274</t>
+          <t>259970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>337533</t>
+          <t>336683</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398705</t>
+          <t>397482</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>348315</t>
+          <t>348785</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>388351</t>
+          <t>387876</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>416568</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>466891</t>
+          <t>467565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>779688</t>
+          <t>780911</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>840860</t>
+          <t>841710</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>27368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39904</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>16931</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63340</t>
+          <t>63483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28917</t>
+          <t>27862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43381</t>
+          <t>42552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56409</t>
+          <t>56286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50614</t>
+          <t>51669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68870</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37913</t>
+          <t>38649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26189</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34085</t>
+          <t>33685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58603</t>
+          <t>58737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80740</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101157</t>
+          <t>101310</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28426</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>41868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114665</t>
+          <t>114531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139183</t>
+          <t>139583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52947</t>
+          <t>55853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83109</t>
+          <t>85799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77670</t>
+          <t>77187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111034</t>
+          <t>109247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148644</t>
+          <t>145954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178806</t>
+          <t>175900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28756</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>43259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180814</t>
+          <t>182601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214178</t>
+          <t>214661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26705</t>
+          <t>25899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45735</t>
+          <t>45818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71493</t>
+          <t>71026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98188</t>
+          <t>98311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105637</t>
+          <t>102899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139804</t>
+          <t>138450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56961</t>
+          <t>56878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75991</t>
+          <t>76797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90212</t>
+          <t>90089</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116907</t>
+          <t>117374</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151292</t>
+          <t>152646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185459</t>
+          <t>188197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126425</t>
+          <t>129224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166912</t>
+          <t>165631</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126816</t>
+          <t>127749</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163998</t>
+          <t>166583</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227792</t>
+          <t>229073</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268279</t>
+          <t>265480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>232694</t>
+          <t>230109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269876</t>
+          <t>268943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127667</t>
+          <t>127896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>172407</t>
+          <t>172620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259328</t>
+          <t>256285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>311950</t>
+          <t>311567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401087</t>
+          <t>400432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>473420</t>
+          <t>470148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>431970</t>
+          <t>431741</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>430055</t>
+          <t>430438</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>482677</t>
+          <t>485720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>828222</t>
+          <t>831494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>900555</t>
+          <t>901210</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>55187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65792</t>
+          <t>65388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32779</t>
+          <t>32396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80293</t>
+          <t>79290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96412</t>
+          <t>96325</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36374</t>
+          <t>35952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47194</t>
+          <t>47163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43784</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58590</t>
+          <t>59059</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>24488</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44369</t>
+          <t>44322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95138</t>
+          <t>95773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110405</t>
+          <t>109907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>22399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>36857</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122101</t>
+          <t>122148</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143745</t>
+          <t>142603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32098</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53713</t>
+          <t>52776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45240</t>
+          <t>46432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61597</t>
+          <t>59022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90562</t>
+          <t>90906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150143</t>
+          <t>151080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171758</t>
+          <t>173719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53806</t>
+          <t>52614</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75474</t>
+          <t>74290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>212340</t>
+          <t>211996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241305</t>
+          <t>243880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,51%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>59891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43616</t>
+          <t>42613</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69022</t>
+          <t>68808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88420</t>
+          <t>86731</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121748</t>
+          <t>121384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84428</t>
+          <t>85330</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106828</t>
+          <t>106832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90528</t>
+          <t>90742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115934</t>
+          <t>116937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183023</t>
+          <t>183387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216351</t>
+          <t>218040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131704</t>
+          <t>128820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>174469</t>
+          <t>172657</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131704</t>
+          <t>128820</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174469</t>
+          <t>172657</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238614</t>
+          <t>240426</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>281379</t>
+          <t>284263</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238614</t>
+          <t>240426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>281379</t>
+          <t>284263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105641</t>
+          <t>105867</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143942</t>
+          <t>143017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>244556</t>
+          <t>245150</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>303683</t>
+          <t>302187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>365506</t>
+          <t>364337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>441255</t>
+          <t>434646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>447386</t>
+          <t>448311</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>485687</t>
+          <t>485461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>468681</t>
+          <t>470177</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527808</t>
+          <t>527214</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>922437</t>
+          <t>929046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>998186</t>
+          <t>999355</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15228</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>23028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>29052</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35111</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>94365</t>
+          <t>106639</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88360</t>
+          <t>99502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98853</t>
+          <t>111365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50093</t>
+          <t>58093</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44574</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54970</t>
+          <t>63179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>144458</t>
+          <t>164732</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136632</t>
+          <t>155744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150956</t>
+          <t>171622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>119225</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>119225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>119225</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171743</t>
+          <t>193784</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>171743</t>
+          <t>193784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171743</t>
+          <t>193784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23383</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>26754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40037</t>
+          <t>42819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>78171</t>
+          <t>86626</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71615</t>
+          <t>79321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83345</t>
+          <t>92693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32663</t>
+          <t>39224</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27977</t>
+          <t>33492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36756</t>
+          <t>43619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>110834</t>
+          <t>125850</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101892</t>
+          <t>117281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>117784</t>
+          <t>133346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>15069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>28366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>29702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33579</t>
+          <t>36046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49368</t>
+          <t>54423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81872</t>
+          <t>90782</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74529</t>
+          <t>83518</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87342</t>
+          <t>96815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>112147</t>
+          <t>123434</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103889</t>
+          <t>114395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119678</t>
+          <t>132772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>153257</t>
+          <t>168818</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>153257</t>
+          <t>168818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153257</t>
+          <t>168818</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78757</t>
+          <t>84332</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66712</t>
+          <t>71276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90009</t>
+          <t>96786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>41716</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109422</t>
+          <t>49056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>117448</t>
+          <t>126048</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46793</t>
+          <t>110790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191239</t>
+          <t>141060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>156979</t>
+          <t>172992</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145727</t>
+          <t>160538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169024</t>
+          <t>186048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>288002</t>
+          <t>89164</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217271</t>
+          <t>81824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317125</t>
+          <t>96096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>444981</t>
+          <t>262156</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>371190</t>
+          <t>247144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>515636</t>
+          <t>277414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>257324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>257324</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>257324</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>562429</t>
+          <t>388204</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>562429</t>
+          <t>388204</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>562429</t>
+          <t>388204</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31418</t>
+          <t>34296</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>26711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>42908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>98262</t>
+          <t>106112</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88972</t>
+          <t>95970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107913</t>
+          <t>116516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>129680</t>
+          <t>140407</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119006</t>
+          <t>127431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143123</t>
+          <t>153035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59014</t>
+          <t>64758</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50936</t>
+          <t>56146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>72343</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>105147</t>
+          <t>112162</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95496</t>
+          <t>101758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114437</t>
+          <t>122304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>164161</t>
+          <t>176920</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150718</t>
+          <t>164292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174835</t>
+          <t>189896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>99054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>203409</t>
+          <t>218274</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203409</t>
+          <t>218274</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203409</t>
+          <t>218274</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>293841</t>
+          <t>317327</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>293841</t>
+          <t>317327</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>293841</t>
+          <t>317327</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,27 +10348,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>146840</t>
+          <t>158279</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>133301</t>
+          <t>144891</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160185</t>
+          <t>172297</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>148985</t>
+          <t>160483</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136667</t>
+          <t>147093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162837</t>
+          <t>174521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>173010</t>
+          <t>185385</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159665</t>
+          <t>171367</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186549</t>
+          <t>198773</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>174069</t>
+          <t>186458</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>160217</t>
+          <t>172420</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186387</t>
+          <t>199848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>319850</t>
+          <t>343664</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319850</t>
+          <t>343664</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>319850</t>
+          <t>343664</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>323054</t>
+          <t>346941</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>323054</t>
+          <t>346941</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>323054</t>
+          <t>346941</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>160818</t>
+          <t>172610</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145831</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180819</t>
+          <t>191081</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>334785</t>
+          <t>363015</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172775</t>
+          <t>341948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>426451</t>
+          <t>385651</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>495602</t>
+          <t>535625</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>318655</t>
+          <t>506797</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>577143</t>
+          <t>564967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>471460</t>
+          <t>522868</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>451459</t>
+          <t>504397</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>486447</t>
+          <t>540858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>679189</t>
+          <t>516681</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>587523</t>
+          <t>494045</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841199</t>
+          <t>537748</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1150650</t>
+          <t>1039549</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1069109</t>
+          <t>1010207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1327597</t>
+          <t>1068377</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>632278</t>
+          <t>695478</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>632278</t>
+          <t>695478</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>632278</t>
+          <t>695478</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1013974</t>
+          <t>879696</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1013974</t>
+          <t>879696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1013974</t>
+          <t>879696</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1646252</t>
+          <t>1575174</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1646252</t>
+          <t>1575174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1646252</t>
+          <t>1575174</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
